--- a/docs/CardioAI_Models_Sheet.xlsx
+++ b/docs/CardioAI_Models_Sheet.xlsx
@@ -8,25 +8,26 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP open items" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Endpoints" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outputs" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auto-labelling" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Annotation" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Automatic audit" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release gates" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demo validation" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eligibility" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP open items" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Endpoints" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outputs" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auto-labelling" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Annotation" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Automatic audit" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release gates" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demo validation" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Endpoints'!$A$2:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Inputs'!$A$2:$N$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Outputs'!$A$2:$E$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Auto-labelling'!$A$2:$F$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Annotation'!$A$2:$D$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Automatic audit'!$A$2:$E$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Release gates'!$A$2:$D$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Demo validation'!$A$2:$L$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Endpoints'!$A$2:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Inputs'!$A$2:$N$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Outputs'!$A$2:$E$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Auto-labelling'!$A$2:$F$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Annotation'!$A$2:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Automatic audit'!$A$2:$E$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Release gates'!$A$2:$D$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Demo validation'!$A$2:$L$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -139,7 +140,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -208,6 +209,10 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -593,7 +598,7 @@
       </c>
       <c r="F4" s="15" t="inlineStr">
         <is>
-          <t>Primary and secondary prevention populations. Adults 18–90 at a landmark outpatient visit with a lipid result in the prior year, 2012–2019.</t>
+          <t>Primary and secondary prevention populations. Adults 18–89 (no pediatric patients) at a landmark outpatient visit with a lipid result in the prior year, 2012–2019.</t>
         </is>
       </c>
       <c r="G4" s="15">
@@ -641,7 +646,7 @@
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>Includes AF-stroke and hemorrhagic stroke models. Adults 18–90 at a landmark outpatient visit with a lipid result in the prior year, 2012–2019.</t>
+          <t>Includes AF-stroke and hemorrhagic stroke models. Adults 18–89 (no pediatric patients) at a landmark outpatient visit with a lipid result in the prior year, 2012–2019.</t>
         </is>
       </c>
       <c r="G5" s="15">
@@ -689,7 +694,7 @@
       </c>
       <c r="F6" s="15" t="inlineStr">
         <is>
-          <t>Separate models for HFrEF and HFpEF. Adults 18–90 at a landmark outpatient visit with a lipid result in the prior year, 2012–2019.</t>
+          <t>Separate models for HFrEF and HFpEF. Adults 18–89 (no pediatric patients) at a landmark outpatient visit with a lipid result in the prior year, 2012–2019.</t>
         </is>
       </c>
       <c r="G6" s="15">
@@ -737,7 +742,7 @@
       </c>
       <c r="F7" s="15" t="inlineStr">
         <is>
-          <t>Guides ICD placement decisions. Adults 18–90 at a landmark outpatient visit with a lipid result in the prior year, 2012–2019.</t>
+          <t>Guides ICD placement decisions. Adults 18–89 (no pediatric patients) at a landmark outpatient visit with a lipid result in the prior year, 2012–2019.</t>
         </is>
       </c>
       <c r="G7" s="15">
@@ -785,7 +790,7 @@
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>Enables targeted screening and early intervention. Excludes patients with AF before index. Adults 18–90 at a landmark outpatient visit with a lipid result in the prior year, 2012–2019.</t>
+          <t>Enables targeted screening and early intervention. Excludes patients with AF before index. Adults 18–89 (no pediatric patients) at a landmark outpatient visit with a lipid result in the prior year, 2012–2019.</t>
         </is>
       </c>
       <c r="G8" s="15">
@@ -815,6 +820,281 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="30" customWidth="1" style="10" min="1" max="1"/>
+    <col width="60" customWidth="1" style="10" min="2" max="2"/>
+    <col width="14" customWidth="1" style="10" min="3" max="3"/>
+    <col width="20" customWidth="1" style="10" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" s="11">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>Training on Mayo Clinic Platform data requires a release in which every gate passed or was waived.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="11">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>Who may waive</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="11">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>Automatic audit resolved</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>All warnings acknowledged, all failures waived (written reason) or fixed</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Data scientist</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="11">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Dataset approved</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Data scientist approval; creates the adjudication sample</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="11">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>All cases final</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>No open reads or unresolved disagreements</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="11">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Inter-reader agreement</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Cohen's κ ≥ 0.6 on ≥10 double reads</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Per outcome</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Lead cardiologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="11">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>PPV of auto-confirmed labels</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>≥ 85% on 50 random cases</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Per outcome</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Lead cardiologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="11">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>NPV of auto-rejected labels</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>≥ 85% on 50 random cases</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Per outcome</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Lead cardiologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="11">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Indeterminate cases</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>≤ 15% of final cases</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Per outcome</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Lead cardiologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="11">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>LVEF / CAC extraction accuracy</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>≥ 90% (weighted)</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Per field</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Data scientist</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Audit trail intact</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Hash chain verifies end to end</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Cannot be waived</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="11">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Release sign-offs</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Data scientist + lead cardiologist, two different people</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Cannot be waived</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:D12"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2200,7 +2480,615 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" style="11" min="1" max="1"/>
+    <col width="16" customWidth="1" style="11" min="2" max="2"/>
+    <col width="62" customWidth="1" style="11" min="3" max="3"/>
+    <col width="22" customWidth="1" style="11" min="4" max="4"/>
+    <col width="18" customWidth="1" style="11" min="5" max="5"/>
+    <col width="24" customWidth="1" style="11" min="6" max="6"/>
+    <col width="36" customWidth="1" style="11" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="48" customHeight="1" s="11">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Who the five calculators are for: Adults aged 18–89 years. Pediatric patients (under 18) are excluded from training, validation and use of all five calculators. The same rules are applied by the cohort SQL, the automatic audit and the calculator app (cardioai_core/schema.py → ELIGIBILITY).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2" s="25" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C2" s="25" t="inlineStr">
+        <is>
+          <t>Criterion</t>
+        </is>
+      </c>
+      <c r="D2" s="25" t="inlineStr">
+        <is>
+          <t>Applies to</t>
+        </is>
+      </c>
+      <c r="E2" s="25" t="inlineStr">
+        <is>
+          <t>Lower bound</t>
+        </is>
+      </c>
+      <c r="F2" s="25" t="inlineStr">
+        <is>
+          <t>Upper bound</t>
+        </is>
+      </c>
+      <c r="G2" s="25" t="inlineStr">
+        <is>
+          <t>Enforced in</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>I1</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>Inclusion</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>Age 18–89 years at the index visit (age ≥ 18.0 and &lt; 90.0)</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>All 5 calculators</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>18 years (inclusive)</t>
+        </is>
+      </c>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>89 years (inclusive; &lt; 90)</t>
+        </is>
+      </c>
+      <c r="G3" s="19" t="inlineStr">
+        <is>
+          <t>cohort SQL; API validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>I2</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>Inclusion</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>An outpatient visit between 2012-01-01 and 2019-12-31 (one index visit per patient, chosen at random among eligible visits)</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>All 5 calculators</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr"/>
+      <c r="F4" s="19" t="inlineStr"/>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>cohort SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>I3</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>Inclusion</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>At least 365 days of observation before the index visit</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>All 5 calculators</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr"/>
+      <c r="F5" s="19" t="inlineStr"/>
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>cohort SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Inclusion</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>Total cholesterol or HDL cholesterol measured in the 365 days before the index visit</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>All 5 calculators</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr"/>
+      <c r="F6" s="19" t="inlineStr"/>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>cohort SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>I5</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Inclusion</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>Recorded sex male or female (the models and published equations are sex-specific)</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>All 5 calculators</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr"/>
+      <c r="F7" s="19" t="inlineStr"/>
+      <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>cohort SQL; API validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>Exclusion</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>Age under 18 at the index visit (pediatric)</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>All 5 calculators</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr"/>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>&lt; 18 years</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
+        <is>
+          <t>cohort SQL; audit (fail); API refuses</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>Exclusion</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>Age 90 or over at the index visit (top-coded in de-identified data)</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>All 5 calculators</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>≥ 90 years</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr"/>
+      <c r="G9" s="19" t="inlineStr">
+        <is>
+          <t>cohort SQL; audit (fail); API refuses</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>Exclusion</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>Sex not recorded as male or female</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>All 5 calculators</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr"/>
+      <c r="F10" s="19" t="inlineStr"/>
+      <c r="G10" s="19" t="inlineStr">
+        <is>
+          <t>cohort SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>Exclusion</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>Death recorded on or before the index date</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>All 5 calculators</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr"/>
+      <c r="F11" s="19" t="inlineStr"/>
+      <c r="G11" s="19" t="inlineStr">
+        <is>
+          <t>cohort SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>Exclusion</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>No observation time after the index date (no follow-up)</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>All 5 calculators</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr"/>
+      <c r="F12" s="19" t="inlineStr"/>
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>cohort SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>E6</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>Exclusion</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>Known atrial fibrillation or flutter at the index visit</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>Atrial Fibrillation</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr"/>
+      <c r="F13" s="19" t="inlineStr"/>
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>AF training labels; API returns 'not applicable'</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>O1</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>Outcome rule</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>Type 2 (supply/demand) MI is not counted as an AMI event (the patient stays in the cohort)</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>AMI</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr"/>
+      <c r="F14" s="19" t="inlineStr"/>
+      <c r="G14" s="19" t="inlineStr">
+        <is>
+          <t>Labelling governance (data/governance.json)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>O2</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>Outcome rule</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>Post-operative AF (≤ 30 days after cardiac surgery) is not counted as new-onset AF (the patient stays in the cohort)</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>AF</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr"/>
+      <c r="F15" s="19" t="inlineStr"/>
+      <c r="G15" s="19" t="inlineStr">
+        <is>
+          <t>Labelling governance (data/governance.json)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>Outcome rule</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Only the first event of each outcome after the index date is counted (the patient stays in the cohort)</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>All 5 calculators</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr"/>
+      <c r="F16" s="19" t="inlineStr"/>
+      <c r="G16" s="19" t="inlineStr">
+        <is>
+          <t>Labelling governance (data/governance.json)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>Reference equation range</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>Pooled Cohort Equations: validated 40–79 years; outside it the app shows the equation as not applicable</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>Reference only</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr"/>
+      <c r="F17" s="19" t="inlineStr"/>
+      <c r="G17" s="19" t="inlineStr">
+        <is>
+          <t>cardioai_core/equations.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>Reference equation range</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>CHARGE-AF: validated 46–94 years (used here up to 89); outside it the app shows the equation as not applicable</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>Reference only</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr"/>
+      <c r="F18" s="19" t="inlineStr"/>
+      <c r="G18" s="19" t="inlineStr">
+        <is>
+          <t>cardioai_core/equations.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>Reference equation range</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>CHA₂DS₂-VASc: validated adults with AF; outside it the app shows the equation as not applicable</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>Reference only</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr"/>
+      <c r="F19" s="19" t="inlineStr"/>
+      <c r="G19" s="19" t="inlineStr">
+        <is>
+          <t>cardioai_core/equations.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>Reference equation range</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>ICD criteria: validated adults; outside it the app shows the equation as not applicable</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>Reference only</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr"/>
+      <c r="F20" s="19" t="inlineStr"/>
+      <c r="G20" s="19" t="inlineStr">
+        <is>
+          <t>cardioai_core/equations.py</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="11" min="1" max="1"/>
@@ -2638,12 +3526,49 @@
       <c r="H12" s="19" t="inlineStr"/>
       <c r="I12" s="19" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>Age top-coding</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>Are ages 90 and over top-coded ("90+") in the de-identified data, and are dates of birth or ages shifted? Confirm the cohort upper bound of 89.</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>The calculators are restricted to adults 18–89; the upper bound assumes ages ≥ 90 are top-coded.</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>Cohort age bounds (cardioai_core/schema.py AGE_MIN / AGE_MAX).</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>Before extraction (Phase 3)</t>
+        </is>
+      </c>
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H13" s="19" t="inlineStr"/>
+      <c r="I13" s="19" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G3:G12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G3:G13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,Asked,Answered,Not applicable"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2651,7 +3576,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3216,7 +4141,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3341,7 +4266,7 @@
       </c>
       <c r="E3" s="15" t="inlineStr">
         <is>
-          <t>18–100</t>
+          <t>18–89 (adults only; under 18 refused)</t>
         </is>
       </c>
       <c r="F3" s="15" t="inlineStr">
@@ -5639,7 +6564,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6807,7 +7732,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7823,7 +8748,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8208,7 +9133,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8406,7 +9331,7 @@
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Age at index outside 18–90</t>
+          <t>Age at index outside 18–89</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
@@ -8861,279 +9786,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="30" customWidth="1" style="10" min="1" max="1"/>
-    <col width="60" customWidth="1" style="10" min="2" max="2"/>
-    <col width="14" customWidth="1" style="10" min="3" max="3"/>
-    <col width="20" customWidth="1" style="10" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1" s="11">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>Training on Mayo Clinic Platform data requires a release in which every gate passed or was waived.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="11">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Gate</t>
-        </is>
-      </c>
-      <c r="B2" s="14" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="C2" s="14" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="D2" s="14" t="inlineStr">
-        <is>
-          <t>Who may waive</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="11">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>Automatic audit resolved</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="inlineStr">
-        <is>
-          <t>All warnings acknowledged, all failures waived (written reason) or fixed</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
-        <is>
-          <t>Data scientist</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="11">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>Dataset approved</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>Data scientist approval; creates the adjudication sample</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D4" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="11">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>All cases final</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>No open reads or unresolved disagreements</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="11">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>Inter-reader agreement</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>Cohen's κ ≥ 0.6 on ≥10 double reads</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>Per outcome</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>Lead cardiologist</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="11">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>PPV of auto-confirmed labels</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>≥ 85% on 50 random cases</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Per outcome</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Lead cardiologist</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="11">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>NPV of auto-rejected labels</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>≥ 85% on 50 random cases</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Per outcome</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>Lead cardiologist</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="11">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>Indeterminate cases</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>≤ 15% of final cases</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>Per outcome</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>Lead cardiologist</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="11">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>LVEF / CAC extraction accuracy</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>≥ 90% (weighted)</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>Per field</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>Data scientist</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>Audit trail intact</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>Hash chain verifies end to end</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>Cannot be waived</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="11">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Release sign-offs</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>Data scientist + lead cardiologist, two different people</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>Cannot be waived</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A2:D12"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
 </file>
--- a/docs/CardioAI_Models_Sheet.xlsx
+++ b/docs/CardioAI_Models_Sheet.xlsx
@@ -3756,7 +3756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="11" min="1" max="1"/>
@@ -3855,11 +3855,19 @@
       </c>
       <c r="G3" s="19" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="H3" s="19" t="inlineStr"/>
-      <c r="I3" s="19" t="inlineStr"/>
+          <t>Partly answered</t>
+        </is>
+      </c>
+      <c r="H3" s="19" t="inlineStr">
+        <is>
+          <t>DIM_PATIENT has one row per record system; PATIENT_CLINIC_NUMBER is the same person across systems (PATIENT_MERGED_FLAG = 'N' gives one row per person). FACT tables carry PATIENT_DK, linked through DIM_PATIENT. Echo ↔ DICOM: link by date + PATIENT_CLINIC_NUMBER. Still open: FACT_ECHO_TEST patient key, echo date and id columns (see #12).</t>
+        </is>
+      </c>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>A. Resnick &amp; T. Stretch (MCP), 21 Oct 2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="19" t="n">
@@ -3929,11 +3937,19 @@
       </c>
       <c r="G5" s="19" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="H5" s="19" t="inlineStr"/>
-      <c r="I5" s="19" t="inlineStr"/>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>Use FACT_DIAGNOSIS.PRIMARY_DIAGNOSIS_FLAG (ICD, Mayo schema), linked to FACT_ENCOUNTERS.ENCOUNTER_TYPE by ENCOUNTER_NUMBER; or claims (FACT_CLAIMS_ITEM_DIAGNOSIS → FACT_CLAIMS.CLAIM_CLASS_NAME inpatient/outpatient). Implemented: primary flag now read from FACT_DIAGNOSIS. Column names to confirm in #13.</t>
+        </is>
+      </c>
+      <c r="I5" s="19" t="inlineStr">
+        <is>
+          <t>A. Resnick &amp; T. Stretch (MCP), 21 Oct 2026</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="19" t="n">
@@ -4003,11 +4019,19 @@
       </c>
       <c r="G7" s="19" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="H7" s="19" t="inlineStr"/>
-      <c r="I7" s="19" t="inlineStr"/>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>FACT_MORTALITY_STATUS combines the Mayo record with third-party death data (Veritas Data Research). Cause of death is not populated: use all-cause death. Last live interaction = completed appointments, immunizations, lab collections, surgical cases. Implemented: deaths and last live interaction from FACT_MORTALITY_STATUS. Coverage start date still open (see #14).</t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="inlineStr">
+        <is>
+          <t>A. Resnick &amp; T. Stretch (MCP), 21 Oct 2026</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="19" t="n">
@@ -4225,11 +4249,167 @@
       </c>
       <c r="G13" s="19" t="inlineStr">
         <is>
+          <t>Partly answered</t>
+        </is>
+      </c>
+      <c r="H13" s="19" t="inlineStr">
+        <is>
+          <t>All dates are shifted by the same amount across a patient's whole record, so windows relative to index are preserved. Still open: are ages 90+ top-coded?</t>
+        </is>
+      </c>
+      <c r="I13" s="19" t="inlineStr">
+        <is>
+          <t>A. Resnick &amp; T. Stretch (MCP), 21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>OMOP ↔ native patient link</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>Which OMOP person column holds PATIENT_CLINIC_NUMBER (person_source_value?), and is there exactly one OMOP person_id per clinic number? Which patient key (PATIENT_DK or PATIENT_CLINIC_NUMBER), date/time and id columns does FACT_ECHO_TEST use?</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>Every native table (echo, diagnosis, mortality) joins to the OMOP cohort through this key; one person split over two person_ids would leak between training and test sets.</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>Native-table extraction (training/native_sources.json); the preflight measures match rates.</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>Before extraction (Phase 3)</t>
+        </is>
+      </c>
+      <c r="G14" s="19" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="H13" s="19" t="inlineStr"/>
-      <c r="I13" s="19" t="inlineStr"/>
+      <c r="H14" s="19" t="n"/>
+      <c r="I14" s="19" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>FACT_DIAGNOSIS columns</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>Which columns hold the patient key, the diagnosis date and the ICD code (with or without the dot), and which PRIMARY_DIAGNOSIS_FLAG value means primary? Does it include ICD-9 codes before Oct 2015?</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>The primary-diagnosis vote matches each OMOP candidate code to FACT_DIAGNOSIS by person, code and date.</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>Auto-labelling (primary_dx) for AMI, stroke, HF, SCD.</t>
+        </is>
+      </c>
+      <c r="F15" s="19" t="inlineStr">
+        <is>
+          <t>Before labelling (Phase 5)</t>
+        </is>
+      </c>
+      <c r="G15" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H15" s="19" t="n"/>
+      <c r="I15" s="19" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>FACT_MORTALITY_STATUS columns</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Which column holds the date of death, and from what year is the third-party (Veritas) death data complete? Is the patient key PATIENT_DK or PATIENT_CLINIC_NUMBER?</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Out-of-Mayo deaths end follow-up and exclude patients dead before index; coverage dates decide which index years are reliable.</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>Follow-up, censoring and exclusion E4 for all 5 calculators.</t>
+        </is>
+      </c>
+      <c r="F16" s="19" t="inlineStr">
+        <is>
+          <t>Before extraction (Phase 3)</t>
+        </is>
+      </c>
+      <c r="G16" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H16" s="19" t="n"/>
+      <c r="I16" s="19" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>LVEF in FACT_ECHO_RESULTS</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>Which FACT_ECHO_RESULTS column holds LVEF, and can one study have several values (e.g. biplane and visual estimate)? (Not yet answered.)</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>A structured LVEF would replace or check the value extracted from echo note text.</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>LVEF input; HF subtype (HFrEF / HFpEF).</t>
+        </is>
+      </c>
+      <c r="F17" s="19" t="inlineStr">
+        <is>
+          <t>Before extraction (Phase 3)</t>
+        </is>
+      </c>
+      <c r="G17" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H17" s="19" t="n"/>
+      <c r="I17" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
